--- a/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
@@ -73,7 +73,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
-    <t>حموي 2 ثانوي  |  AMPHI  |  2AS  |  عبد السلام حموي</t>
+    <t>حموي 2 ثانوي  |  AMPHI  |  2AS  |  حموي عبد السلام</t>
   </si>
   <si>
     <t>class_id=7</t>

--- a/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
@@ -20,49 +20,91 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:26097a7a-6ad2-4323-b5dc-179bf5be3ddd</t>
+          <t>student_id:bf0d9bff-bfa3-4a01-b59d-137d935308d5</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:c25f0551-3205-4c3d-a755-5e7284f14513</t>
+          <t>student_id:d075c953-d14e-4cbe-a3c0-c15ea168390a</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:0f1104bd-9939-4e36-a395-ce65950835cb</t>
+          <t>student_id:58788436-d90d-4aaa-b54b-f506d0c5cfa7</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:67930a0d-a691-488c-8c4c-35f3d8842dbf</t>
+          <t>student_id:399a5570-e979-4d5b-a709-c544a14bbefe</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:a47bbc7b-4a14-45e5-b755-f0ab2e34d1d5</t>
+          <t>student_id:c1c18b3e-a468-49a1-b19b-f23fcc1ddc75</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:66cf83d8-0d83-4cc8-ba82-cf82b411c760</t>
+          <t>student_id:8fac8263-9f8b-4241-af14-fe43fb54f4c2</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:a55310f5-ab4c-468b-8bf3-4f4e44720543</t>
+          <t>student_id:86f172fd-9b4f-440c-bf3a-53f0ccaeca6a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <t>student_id:50d0c748-0b38-47e2-a95f-64ed6193e057</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <t>student_id:9bfb5786-c84a-4522-a851-8089d3fbc154</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <t>student_id:994b3960-5d41-45f2-88a6-1ecb2e9b90a7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:801cf6e6-ede8-4b27-ba45-454d808cb699</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e0a52794-6e5b-4fb3-8b77-988aeb1662d8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:c115d24c-bb6b-4514-9c40-cc628ad3cf89</t>
         </r>
       </text>
     </comment>
@@ -71,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>حموي 2 ثانوي  |  AMPHI  |  2AS  |  حموي عبد السلام</t>
   </si>
@@ -94,12 +136,18 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>05/09/2026</t>
+    <t>26/09/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>يزيد لينا</t>
+  </si>
+  <si>
+    <t>مشري لجين</t>
+  </si>
+  <si>
     <t>لخضاري لجين</t>
   </si>
   <si>
@@ -109,16 +157,28 @@
     <t>بومحراث إسحاق</t>
   </si>
   <si>
+    <t>عيون سهى ملاك</t>
+  </si>
+  <si>
     <t>زيبوش اشواق</t>
   </si>
   <si>
-    <t>يزيد لينا</t>
-  </si>
-  <si>
-    <t>مشري لجين</t>
-  </si>
-  <si>
-    <t>عيون سهى ملاك</t>
+    <t>بوناح سارة مرام</t>
+  </si>
+  <si>
+    <t>بن طوبال لؤي</t>
+  </si>
+  <si>
+    <t>حركاتي ادم</t>
+  </si>
+  <si>
+    <t>زمور شيماء</t>
+  </si>
+  <si>
+    <t>حماني نسرين</t>
+  </si>
+  <si>
+    <t>نموشي اية</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -638,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -763,7 +823,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>208</v>
+        <v>376</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>9</v>
@@ -807,7 +867,7 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>209</v>
+        <v>377</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>10</v>
@@ -851,7 +911,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>210</v>
+        <v>378</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
@@ -895,7 +955,7 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>212</v>
+        <v>379</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>12</v>
@@ -939,7 +999,7 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>547</v>
+        <v>380</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>13</v>
@@ -983,7 +1043,7 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>548</v>
+        <v>381</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
@@ -1027,7 +1087,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>549</v>
+        <v>382</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>15</v>
@@ -1066,6 +1126,270 @@
         <v>0</v>
       </c>
       <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>383</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>384</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>385</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>386</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>387</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>388</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1093,7 +1417,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1103,12 +1427,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -1118,27 +1442,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1148,12 +1472,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1163,7 +1487,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_2_ثانوي.xlsx
@@ -108,12 +108,138 @@
         </r>
       </text>
     </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <t>student_id:6eb5e29c-8e60-4130-af22-5e34fdd483a4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
+          <t>student_id:11ca1679-ab61-464a-b923-80842dd79263</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <t>student_id:cafa7466-0167-42a7-af93-ac823bda60b4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <t>student_id:c5987ba7-4d75-451e-a467-68ab43535941</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e142d54a-19d1-4aea-b2be-47a4c6d353cd</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5a95d658-fe47-4db8-8295-57e9c194dfc7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0">
+      <text>
+        <r>
+          <t>student_id:cf2535cd-747b-4e07-8ba7-880bee0d3efd</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3b873a2e-2692-4988-867e-ea72eaef4c1f</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0">
+      <text>
+        <r>
+          <t>student_id:0c890769-1989-44f9-8942-b2729502b612</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e5da2529-43fe-453e-94f9-9a4aa8461635</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0">
+      <text>
+        <r>
+          <t>student_id:b6785ad7-b175-4281-bd1a-c70acb193d1d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f6a215d4-718f-499e-a159-c75b09b2d55c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0">
+      <text>
+        <r>
+          <t>student_id:d6ff5a55-a5a1-47c0-99f3-32d9da379522</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0">
+      <text>
+        <r>
+          <t>student_id:731c91d4-f06b-4574-b88d-81f72537cbf0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <t>student_id:d960acd9-45ea-4e65-8a19-60a154e783e0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <t>student_id:25629b09-4634-42df-88c6-cd898a3f0feb</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0">
+      <text>
+        <r>
+          <t>student_id:2898f9d3-84fb-46de-a779-b45f2c3fb264</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f61e6a48-1b9c-4b49-8db0-cf87515c3571</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>حموي 2 ثانوي  |  AMPHI  |  2AS  |  حموي عبد السلام</t>
   </si>
@@ -127,6 +253,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -136,7 +265,7 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>26/09/2026</t>
+    <t>03/10/2026</t>
   </si>
   <si>
     <t/>
@@ -181,6 +310,60 @@
     <t>نموشي اية</t>
   </si>
   <si>
+    <t>خنيو لجين</t>
+  </si>
+  <si>
+    <t>العايب مندر</t>
+  </si>
+  <si>
+    <t>مصباح شعيب</t>
+  </si>
+  <si>
+    <t>صنهاجي رزان اسيل</t>
+  </si>
+  <si>
+    <t>سيود تسنيم</t>
+  </si>
+  <si>
+    <t>سطانجي دورصاف</t>
+  </si>
+  <si>
+    <t>طراش مندر</t>
+  </si>
+  <si>
+    <t>بوستة صوفيا</t>
+  </si>
+  <si>
+    <t>مطمور جمانة</t>
+  </si>
+  <si>
+    <t>بن دكوم عبد الرحمان</t>
+  </si>
+  <si>
+    <t>بوفولة ابتهال</t>
+  </si>
+  <si>
+    <t>عماري  جواد</t>
+  </si>
+  <si>
+    <t>تيطاوني رقية</t>
+  </si>
+  <si>
+    <t>لبريمة سيرين</t>
+  </si>
+  <si>
+    <t>بلايزي  فادي</t>
+  </si>
+  <si>
+    <t>حراق تسنيم</t>
+  </si>
+  <si>
+    <t>قندوز  محمد</t>
+  </si>
+  <si>
+    <t>بوصنيجة انس</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -208,7 +391,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -698,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -724,7 +910,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -734,10 +920,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -779,46 +968,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -826,7 +1015,7 @@
         <v>376</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -870,7 +1059,7 @@
         <v>377</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -914,7 +1103,7 @@
         <v>378</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -958,7 +1147,7 @@
         <v>379</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1002,7 +1191,7 @@
         <v>380</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1046,7 +1235,7 @@
         <v>381</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1090,7 +1279,7 @@
         <v>382</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1134,7 +1323,7 @@
         <v>383</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1178,7 +1367,7 @@
         <v>384</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1222,7 +1411,7 @@
         <v>385</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1266,7 +1455,7 @@
         <v>386</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -1310,7 +1499,7 @@
         <v>387</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1354,7 +1543,7 @@
         <v>388</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -1390,6 +1579,798 @@
         <v>0</v>
       </c>
       <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>453</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>724</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>734</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>834</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>875</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>915</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>916</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>917</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>918</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>919</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>920</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>921</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>922</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>923</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>924</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>925</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>926</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>927</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1409,7 +2390,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1417,77 +2398,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
